--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6592A7-486C-417F-B825-7993417F2C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186CB4AA-4FB0-4BB0-B344-726E6A63F66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>StoryID</t>
   </si>
@@ -160,6 +160,14 @@
   </si>
   <si>
     <t>不对，我还要好好分析</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/clinic/spring.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -766,8 +774,12 @@
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="F2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="H2" s="14" t="s">
         <v>29</v>
       </c>

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186CB4AA-4FB0-4BB0-B344-726E6A63F66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7941160-4285-4DCF-B57F-67B2DC253E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>StoryID</t>
   </si>
@@ -170,16 +159,23 @@
     <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/shi_zi_before</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -193,7 +189,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -214,7 +210,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -230,6 +226,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -316,8 +320,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -333,9 +335,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -613,24 +617,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -643,36 +648,39 @@
       <c r="D1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="16" t="s">
         <v>18</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -692,25 +700,28 @@
       <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="1" t="b">
+      <c r="J2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="C3" s="12"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="C4" s="12"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="C5" s="12"/>
+    <row r="3" spans="1:13" ht="18">
+      <c r="C3" s="10"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:13" ht="18">
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:13" ht="18">
+      <c r="C5" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -723,14 +734,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -780,17 +791,13 @@
       <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="12" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="8"/>
       <c r="E3" s="2"/>
@@ -799,12 +806,8 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -813,9 +816,7 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
+      <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="2"/>
@@ -825,9 +826,7 @@
       <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
+      <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="8"/>
@@ -837,9 +836,7 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
+      <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="2"/>
@@ -849,9 +846,7 @@
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
+      <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="8"/>
@@ -861,9 +856,7 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
+      <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="2"/>
@@ -873,9 +866,7 @@
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
+      <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
@@ -885,9 +876,7 @@
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
+      <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="2"/>
@@ -897,9 +886,7 @@
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
+      <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="8"/>
@@ -909,9 +896,7 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
+      <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="2"/>
@@ -921,9 +906,7 @@
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
+      <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
@@ -933,38 +916,34 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
+      <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="14"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="2"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="15"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
+      <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="2"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="15"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="14"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="16"/>
+      <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7941160-4285-4DCF-B57F-67B2DC253E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875658F8-0680-47D6-805A-C0BAEED215D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -163,7 +163,7 @@
     <t>ClinicNpcPortraitPath</t>
   </si>
   <si>
-    <t>res://Assets/Portrait/StoryNpc/shi_zi_before</t>
+    <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_before.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -704,7 +704,7 @@
         <v>33</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>22</v>

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{875658F8-0680-47D6-805A-C0BAEED215D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A988D0D3-CB0E-4036-8ACB-2D2ED6F6C324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
   <si>
     <t>StoryID</t>
   </si>
@@ -137,9 +148,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>story_npc_treatment_failed</t>
-  </si>
-  <si>
     <t>005_03</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -148,10 +156,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>不对，我还要好好分析</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>res://Assets/Background/clinic/spring.png</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -164,6 +168,46 @@
   </si>
   <si>
     <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_before.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>story_npc_failed_over</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>世子</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>咳咳咳，啊…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楚恭王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>right</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>我的儿，你怎么了！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哎呀，这个…王爷你听我解释…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>来人！把这个挨千刀的江湖骗子给我叉出去剁了！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>不好！啊啊啊啊！！！</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -171,11 +215,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -189,7 +233,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -210,7 +254,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -235,6 +279,13 @@
       <color theme="1"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -291,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -337,9 +388,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -618,24 +672,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.1328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:13">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -664,7 +718,7 @@
         <v>18</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>19</v>
@@ -676,15 +730,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:13">
       <c r="A2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>28</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>23</v>
@@ -701,7 +755,7 @@
         <v>24</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>0</v>
@@ -713,14 +767,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:13">
       <c r="C3" s="10"/>
       <c r="K3" s="11"/>
     </row>
-    <row r="4" spans="1:13" ht="18">
+    <row r="4" spans="1:13">
       <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:13" ht="18">
+    <row r="5" spans="1:13">
       <c r="C5" s="10"/>
     </row>
   </sheetData>
@@ -731,17 +785,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -778,88 +832,136 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
+      <c r="C2" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="1"/>
+      <c r="H3" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="1"/>
+      <c r="H4" s="12" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="H5" s="12" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="1"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="2"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -889,7 +991,7 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="8"/>
+      <c r="D12" s="2"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -899,7 +1001,7 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -918,17 +1020,17 @@
     <row r="15" spans="1:8">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="12"/>
+      <c r="C15" s="1"/>
       <c r="D15" s="2"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="13"/>
+      <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="C16" s="12"/>
       <c r="D16" s="2"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -936,24 +1038,24 @@
       <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="3"/>
+      <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="12"/>
+      <c r="C17" s="1"/>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="14"/>
+      <c r="H17" s="13"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="2"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="14"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="3"/>
@@ -1015,6 +1117,16 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
     </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A988D0D3-CB0E-4036-8ACB-2D2ED6F6C324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA3C6A3-4D6C-4828-9D16-9042A95632B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -219,7 +219,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -233,7 +233,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -254,7 +254,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -393,7 +393,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -672,24 +672,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="53.9296875" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -730,7 +730,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
@@ -767,14 +767,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" ht="18">
       <c r="C3" s="10"/>
       <c r="K3" s="11"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" ht="18">
       <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" ht="18">
       <c r="C5" s="10"/>
     </row>
   </sheetData>
@@ -788,14 +788,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA3C6A3-4D6C-4828-9D16-9042A95632B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B34AE4D-BBFF-4995-959A-5AD5131B0DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,17 +20,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -758,7 +747,7 @@
         <v>31</v>
       </c>
       <c r="K2" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>22</v>

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B34AE4D-BBFF-4995-959A-5AD5131B0DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA3024A-9972-4AD2-965F-CCAE043E580B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -156,10 +156,6 @@
     <t>ClinicNpcPortraitPath</t>
   </si>
   <si>
-    <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_before.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>story_npc_failed_over</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -197,6 +193,10 @@
   </si>
   <si>
     <t>不好！啊啊啊啊！！！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>before</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -727,7 +727,7 @@
         <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>23</v>
@@ -743,9 +743,7 @@
       <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="J2" s="2"/>
       <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
@@ -822,12 +820,14 @@
         <v>6</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>41</v>
+      </c>
       <c r="F2" s="8" t="s">
         <v>29</v>
       </c>
@@ -835,7 +835,7 @@
         <v>28</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -846,10 +846,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
@@ -857,7 +857,7 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -879,7 +879,7 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -890,10 +890,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
@@ -901,7 +901,7 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -923,7 +923,7 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DA3024A-9972-4AD2-965F-CCAE043E580B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257C0380-2320-4E0D-982F-27C23DDF78C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4237" yWindow="4057" windowWidth="21601" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -145,10 +145,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Background/clinic/spring.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -197,6 +193,10 @@
   </si>
   <si>
     <t>before</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/003/003_04.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -707,7 +707,7 @@
         <v>18</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>19</v>
@@ -727,7 +727,7 @@
         <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>23</v>
@@ -820,22 +820,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -846,18 +846,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -875,11 +875,11 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -890,18 +890,18 @@
         <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -919,11 +919,11 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257C0380-2320-4E0D-982F-27C23DDF78C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20F8998-BC30-4DBC-85FD-E97936DCF8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4237" yWindow="4057" windowWidth="21601" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -199,6 +210,14 @@
     <t>res://Assets/Background/003/003_04.png</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>005_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -208,7 +227,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -222,7 +241,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -243,7 +262,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -331,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -380,9 +399,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -660,25 +682,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="53.9296875" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="53.875" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:14">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -698,28 +721,31 @@
         <v>15</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:14">
       <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
@@ -733,36 +759,87 @@
         <v>23</v>
       </c>
       <c r="E2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="1" t="b">
+      <c r="K2" s="2"/>
+      <c r="L2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:14">
       <c r="C3" s="10"/>
-      <c r="K3" s="11"/>
-    </row>
-    <row r="4" spans="1:13" ht="18">
+      <c r="G3" s="18"/>
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="C4" s="10"/>
-    </row>
-    <row r="5" spans="1:13" ht="18">
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="C5" s="10"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="7:7">
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="7:7">
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="7:7">
+      <c r="G20" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -775,14 +852,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20F8998-BC30-4DBC-85FD-E97936DCF8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91EED68-C3F8-4917-84F6-886C7CDAAE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>StoryID</t>
   </si>
@@ -160,9 +160,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
     <t>story_npc_failed_over</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -215,7 +212,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>005_01</t>
+    <t>ClinicNpcPortraitPath</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -687,15 +684,14 @@
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="53.875" customWidth="1"/>
+    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.625" customWidth="1"/>
     <col min="13" max="13" width="13.5" customWidth="1"/>
     <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
@@ -721,7 +717,7 @@
         <v>15</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>16</v>
@@ -733,7 +729,7 @@
         <v>18</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L1" s="6" t="s">
         <v>19</v>
@@ -753,7 +749,7 @@
         <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>23</v>
@@ -764,9 +760,7 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="G2" s="5"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="s">
@@ -897,22 +891,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -923,10 +917,10 @@
         <v>6</v>
       </c>
       <c r="C3" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
@@ -934,7 +928,7 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -956,7 +950,7 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -967,10 +961,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
@@ -978,7 +972,7 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1000,7 +994,7 @@
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91EED68-C3F8-4917-84F6-886C7CDAAE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043860A1-6A5B-4C38-8480-6FDC008F0762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -214,6 +214,10 @@
   <si>
     <t>ClinicNpcPortraitPath</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerCureCount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -294,7 +298,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,6 +320,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -397,6 +407,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -679,25 +695,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -710,38 +727,41 @@
       <c r="D1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
@@ -754,86 +774,87 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="1">
-        <v>0</v>
+      <c r="E2" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1"/>
+      <c r="G2" s="1">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="1" t="b">
+      <c r="L2" s="1"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="C3" s="10"/>
-      <c r="G3" s="18"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="H3" s="18"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="C4" s="10"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="H4" s="18"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="C5" s="10"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="7:7">
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" spans="7:7">
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="7:7">
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" spans="7:7">
-      <c r="G20" s="18"/>
+      <c r="H5" s="18"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="H6" s="18"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="H7" s="18"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="H8" s="18"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="H14" s="18"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="H16" s="18"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043860A1-6A5B-4C38-8480-6FDC008F0762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2689B29-D7BF-4DEA-A796-A0BB492547FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>StoryID</t>
   </si>
@@ -87,12 +76,6 @@
   </si>
   <si>
     <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>EntryId</t>
   </si>
   <si>
     <t>NpcID</t>
@@ -219,6 +202,22 @@
     <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -228,7 +227,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -242,7 +241,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -263,7 +262,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -417,7 +416,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -695,26 +694,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -728,54 +730,60 @@
         <v>13</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="K1" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="16" t="s">
+      <c r="M1" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="M1" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="N1" s="19" t="s">
+      <c r="Q1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="19" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -787,61 +795,63 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="1" t="b">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="C3" s="10"/>
       <c r="H3" s="18"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="C4" s="10"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="C5" s="10"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="H16" s="18"/>
     </row>
     <row r="17" spans="8:8">
@@ -867,14 +877,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -912,22 +922,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -938,18 +948,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -960,18 +970,18 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -982,18 +992,18 @@
         <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1004,18 +1014,18 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2689B29-D7BF-4DEA-A796-A0BB492547FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17476EC-4685-4135-8E2D-2E06704B095C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -227,7 +238,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -241,7 +252,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -262,7 +273,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -416,7 +427,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -695,25 +706,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -797,7 +808,9 @@
       <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1"/>
+      <c r="L2" s="1">
+        <v>1</v>
+      </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -877,14 +890,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E17476EC-4685-4135-8E2D-2E06704B095C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605A63B6-0B1D-4855-BF07-4BF4A35BDB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -210,10 +210,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>TriggerCureCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Reputation</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -227,6 +223,10 @@
   </si>
   <si>
     <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>005_01</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -705,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
@@ -719,15 +719,14 @@
     <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -747,13 +746,13 @@
         <v>14</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>39</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>15</v>
@@ -761,26 +760,23 @@
       <c r="K1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>41</v>
-      </c>
-      <c r="M1" s="20" t="s">
-        <v>40</v>
       </c>
       <c r="N1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="20" t="s">
-        <v>43</v>
+      <c r="O1" s="19" t="s">
+        <v>17</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="19" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
@@ -796,75 +792,70 @@
       <c r="E2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1">
-        <v>1</v>
-      </c>
+      <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="1" t="b">
+      <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="P2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="18"/>
-      <c r="P3" s="11"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:16">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:16">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:16">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:16">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:16">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:16">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:16">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:16">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:16">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:16">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:16">
       <c r="H16" s="18"/>
     </row>
     <row r="17" spans="8:8">

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605A63B6-0B1D-4855-BF07-4BF4A35BDB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14EB4CA-58E3-40A2-84E7-94096F9E2671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>StoryID</t>
   </si>
@@ -92,10 +81,6 @@
     <t>NpcID</t>
   </si>
   <si>
-    <t>TriggerNpcID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
@@ -109,10 +94,6 @@
   </si>
   <si>
     <t>night</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>shi_zi</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -229,6 +210,10 @@
     <t>005_01</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -238,7 +223,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -252,7 +237,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -273,7 +258,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -427,7 +412,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -706,24 +691,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -740,68 +725,66 @@
         <v>13</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="15" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="M1" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="O1" s="19" t="s">
-        <v>17</v>
-      </c>
       <c r="P1" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -881,14 +864,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -926,22 +909,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -952,18 +935,18 @@
         <v>6</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -974,18 +957,18 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -996,18 +979,18 @@
         <v>6</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1018,18 +1001,18 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:8">

--- a/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
+++ b/DataTables/DetailText/剧情/005_03治愈世子失败.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14EB4CA-58E3-40A2-84E7-94096F9E2671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC29DB22-1701-4C18-BC6A-CCF13349611C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -179,10 +190,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Background/003/003_04.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>TriggerStoryID</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -213,6 +220,52 @@
   <si>
     <t>Disease</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_04.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -223,7 +276,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -237,7 +290,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -258,7 +311,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -412,7 +465,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -691,24 +744,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -731,28 +784,28 @@
         <v>14</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>42</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L1" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>39</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>40</v>
       </c>
       <c r="O1" s="19" t="s">
         <v>16</v>
@@ -780,7 +833,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -864,14 +917,14 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -921,7 +974,7 @@
         <v>24</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>27</v>
